--- a/docs/informes/edistribucion_generacion_2026-09-03.xlsx
+++ b/docs/informes/edistribucion_generacion_2026-09-03.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>30/09/2026 09:52</t>
+          <t>30/09/2026 10:08</t>
         </is>
       </c>
     </row>

--- a/docs/informes/edistribucion_generacion_2026-09-03.xlsx
+++ b/docs/informes/edistribucion_generacion_2026-09-03.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026 09:56</t>
+          <t>02/10/2026 12:28</t>
         </is>
       </c>
     </row>

--- a/docs/informes/edistribucion_generacion_2026-09-03.xlsx
+++ b/docs/informes/edistribucion_generacion_2026-09-03.xlsx
@@ -512,7 +512,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>02/10/2026 12:28</t>
+          <t>02/10/2026 13:43</t>
         </is>
       </c>
     </row>
